--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-11T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Level</t>
@@ -202,6 +202,12 @@
   </si>
   <si>
     <t>UAT Participant XYK</t>
+  </si>
+  <si>
+    <t>IOM</t>
+  </si>
+  <si>
+    <t>UAT Participant IOM</t>
   </si>
 </sst>
 </file>
@@ -511,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -660,6 +666,18 @@
       </c>
       <c r="D12" s="2"/>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-03T08:24:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>Level</t>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>UAT Participant IOM</t>
+  </si>
+  <si>
+    <t>XXQ</t>
+  </si>
+  <si>
+    <t>UAT Participant XXQ</t>
   </si>
 </sst>
 </file>
@@ -517,7 +523,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -678,6 +684,18 @@
       </c>
       <c r="D13" s="2"/>
     </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:24:29+00:00</t>
+    <t>2026-07-06T11:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:52:41+00:00</t>
+    <t>2026-07-30T11:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="65">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T11:57:48+00:00</t>
+    <t>2026-08-27T05:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>Level</t>
@@ -141,13 +141,16 @@
     <t>1</t>
   </si>
   <si>
+    <t>IOM</t>
+  </si>
+  <si>
     <t>UAT Participant WHO</t>
   </si>
   <si>
     <t>XXA</t>
   </si>
   <si>
-    <t>UAT Participant XXA</t>
+    <t>Geneva</t>
   </si>
   <si>
     <t>XXB</t>
@@ -174,22 +177,25 @@
     <t>UAT Participant XXO</t>
   </si>
   <si>
+    <t>XXQ</t>
+  </si>
+  <si>
+    <t>Test Locality</t>
+  </si>
+  <si>
     <t>XXS</t>
   </si>
   <si>
-    <t>UAT Participant XXS</t>
+    <t>XXT</t>
   </si>
   <si>
     <t>XXU</t>
   </si>
   <si>
-    <t>UAT Participant XXU</t>
-  </si>
-  <si>
     <t>XXV</t>
   </si>
   <si>
-    <t>UAT Participant XXV</t>
+    <t>test city</t>
   </si>
   <si>
     <t>XXX</t>
@@ -201,19 +207,7 @@
     <t>XYK</t>
   </si>
   <si>
-    <t>UAT Participant XYK</t>
-  </si>
-  <si>
-    <t>IOM</t>
-  </si>
-  <si>
-    <t>UAT Participant IOM</t>
-  </si>
-  <si>
-    <t>XXQ</t>
-  </si>
-  <si>
-    <t>UAT Participant XXQ</t>
+    <t>INDIA</t>
   </si>
 </sst>
 </file>
@@ -523,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -545,7 +539,7 @@
         <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
         <v>42</v>
@@ -557,10 +551,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>44</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -569,10 +563,10 @@
         <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="C4" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>46</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -581,10 +575,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -593,10 +587,10 @@
         <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>50</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -605,10 +599,10 @@
         <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -617,10 +611,10 @@
         <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>54</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -629,10 +623,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>55</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>56</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -641,10 +635,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -653,10 +647,10 @@
         <v>41</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -665,10 +659,10 @@
         <v>41</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2"/>
     </row>
@@ -677,10 +671,10 @@
         <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2"/>
     </row>
@@ -689,12 +683,24 @@
         <v>41</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/trust/CodeSystem-Participants-UAT.xlsx
+++ b/trust/CodeSystem-Participants-UAT.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.1</t>
+    <t>1.7.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T05:52:17+00:00</t>
+    <t>2026-09-03T12:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
